--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{977CB467-9A10-4206-A10D-138C68963F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F79ACC-56A0-4E19-A219-EA02126292EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>46234</v>
+        <v>46265</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2116,15 +2116,15 @@
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>41302</v>
+        <v>47175</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>5953</v>
+        <v>6775</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>7303</v>
+        <v>8355</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2133,15 +2133,15 @@
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>24556</v>
+        <v>28048</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>2029</v>
+        <v>2267</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>3474</v>
+        <v>3953</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2150,15 +2150,15 @@
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>63569</v>
+        <v>72486</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>5624</v>
+        <v>6586</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>5626</v>
+        <v>6469</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,15 +2167,15 @@
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>1280</v>
+        <v>1459</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>551</v>
+        <v>650</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>96</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2184,15 +2184,15 @@
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>45754</v>
+        <v>51907</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>5615</v>
+        <v>6497</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>4992</v>
+        <v>5693</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,15 +2201,15 @@
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>5975</v>
+        <v>6856</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>965</v>
+        <v>1106</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>1032</v>
+        <v>1232</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2218,15 +2218,15 @@
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>3780</v>
+        <v>4231</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>893</v>
+        <v>1005</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>704</v>
+        <v>797</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2235,15 +2235,15 @@
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>2117</v>
+        <v>2493</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>285</v>
+        <v>320</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>160</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>382</v>
+        <v>432</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>112</v>
+        <v>137</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
@@ -2286,15 +2286,15 @@
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>271</v>
+        <v>328</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>239</v>
+        <v>288</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2303,15 +2303,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>1244</v>
+        <v>1431</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>691</v>
+        <v>803</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>340</v>
+        <v>381</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2320,15 +2320,15 @@
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>5100</v>
+        <v>5772</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>1592</v>
+        <v>1833</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>854</v>
+        <v>959</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2337,15 +2337,15 @@
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>2304</v>
+        <v>2617</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>1556</v>
+        <v>1836</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>374</v>
+        <v>418</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2354,15 +2354,15 @@
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>2126</v>
+        <v>2454</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>318</v>
+        <v>369</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2371,15 +2371,15 @@
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>14589</v>
+        <v>16676</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>2259</v>
+        <v>2676</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>3300</v>
+        <v>3851</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2388,15 +2388,15 @@
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>1300</v>
+        <v>1438</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>472</v>
+        <v>546</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>308</v>
+        <v>347</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2405,15 +2405,15 @@
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>15671</v>
+        <v>17898</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>1705</v>
+        <v>1904</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>2594</v>
+        <v>2931</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2422,15 +2422,15 @@
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>142</v>
+        <v>182</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>225</v>
+        <v>258</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
-        <v>7</v>
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2439,15 +2439,15 @@
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>14615</v>
+        <v>16821</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>2137</v>
+        <v>2440</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>2824</v>
+        <v>3292</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2456,15 +2456,15 @@
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>2632</v>
+        <v>2935</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>1182</v>
+        <v>1354</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>456</v>
+        <v>511</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2473,15 +2473,15 @@
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>20296</v>
+        <v>23552</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>3008</v>
+        <v>3409</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>3390</v>
+        <v>4004</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2490,15 +2490,15 @@
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>86910</v>
+        <v>100614</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>7179</v>
+        <v>8284</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>8967</v>
+        <v>10394</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2507,15 +2507,15 @@
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>4207</v>
+        <v>4962</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>1720</v>
+        <v>2011</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>850</v>
+        <v>969</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2541,15 +2541,15 @@
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>4689</v>
+        <v>5250</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>918</v>
+        <v>1061</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>1054</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2558,15 +2558,15 @@
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>3388</v>
+        <v>3864</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>594</v>
+        <v>688</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>847</v>
+        <v>989</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2575,15 +2575,15 @@
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>20868</v>
+        <v>23049</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>2456</v>
+        <v>2832</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>3757</v>
+        <v>4200</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2592,15 +2592,15 @@
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>348</v>
+        <v>400</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>177</v>
+        <v>194</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2609,15 +2609,15 @@
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>2935</v>
+        <v>3119</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>1503</v>
+        <v>1751</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>545</v>
+        <v>558</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2626,15 +2626,15 @@
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>12398</v>
+        <v>14253</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>2712</v>
+        <v>3156</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>2394</v>
+        <v>2788</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2643,15 +2643,15 @@
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>9047</v>
+        <v>10384</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>1700</v>
+        <v>2036</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>1738</v>
+        <v>2003</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2660,15 +2660,15 @@
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>4673</v>
+        <v>5444</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>607</v>
+        <v>719</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
-        <v>824</v>
+        <v>943</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -2677,15 +2677,15 @@
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>46568</v>
+        <v>53844</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>8010</v>
+        <v>9222</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>5959</v>
+        <v>6981</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2694,15 +2694,15 @@
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>6853</v>
+        <v>7713</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>3012</v>
+        <v>3516</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>928</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2711,15 +2711,15 @@
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>27866</v>
+        <v>31902</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>1831</v>
+        <v>2118</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>2930</v>
+        <v>3405</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2728,15 +2728,15 @@
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>2357</v>
+        <v>2558</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>973</v>
+        <v>1135</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>259</v>
+        <v>290</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2745,15 +2745,15 @@
       </c>
       <c r="B40" s="6">
         <f>SUM(January:December!B40)</f>
-        <v>2009</v>
+        <v>2547</v>
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>294</v>
+        <v>348</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2762,15 +2762,15 @@
       </c>
       <c r="B41" s="7">
         <f>SUM(January:December!B41)</f>
-        <v>8969</v>
+        <v>10640</v>
       </c>
       <c r="C41" s="7">
         <f>SUM(January:December!C41)</f>
-        <v>428</v>
+        <v>514</v>
       </c>
       <c r="D41" s="7">
         <f>SUM(January:December!D41)</f>
-        <v>413</v>
+        <v>422</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2779,15 +2779,15 @@
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>174</v>
+        <v>217</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="D42" s="6">
         <f>SUM(January:December!D42)</f>
-        <v>17</v>
+        <v>24</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2796,15 +2796,15 @@
       </c>
       <c r="B43" s="7">
         <f>SUM(January:December!B43)</f>
-        <v>1137</v>
+        <v>1485</v>
       </c>
       <c r="C43" s="7">
         <f>SUM(January:December!C43)</f>
-        <v>116</v>
+        <v>144</v>
       </c>
       <c r="D43" s="7">
         <f>SUM(January:December!D43)</f>
-        <v>81</v>
+        <v>87</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2813,15 +2813,15 @@
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>1671</v>
+        <v>1813</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>492</v>
+        <v>575</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>929</v>
+        <v>998</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2830,15 +2830,15 @@
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>3059</v>
+        <v>3314</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>1067</v>
+        <v>1216</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>279</v>
+        <v>322</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2847,15 +2847,15 @@
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>13277</v>
+        <v>15373</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>3173</v>
+        <v>3641</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>2654</v>
+        <v>3109</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2864,15 +2864,15 @@
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>28992</v>
+        <v>32818</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>3441</v>
+        <v>4012</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>3988</v>
+        <v>4594</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,15 +2881,15 @@
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>12850</v>
+        <v>14526</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>2974</v>
+        <v>3432</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>1248</v>
+        <v>1415</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2898,15 +2898,15 @@
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>6493</v>
+        <v>7685</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>1283</v>
+        <v>1456</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>1601</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2915,15 +2915,15 @@
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>30247</v>
+        <v>34490</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>2836</v>
+        <v>3323</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>4722</v>
+        <v>5346</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2932,15 +2932,15 @@
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>3524</v>
+        <v>3957</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>806</v>
+        <v>940</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>739</v>
+        <v>848</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2949,15 +2949,15 @@
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>9228</v>
+        <v>10319</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>1875</v>
+        <v>2191</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>2323</v>
+        <v>2615</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2966,15 +2966,15 @@
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>1323</v>
+        <v>1427</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>1179</v>
+        <v>1350</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>501</v>
+        <v>559</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2983,15 +2983,15 @@
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>1560</v>
+        <v>1732</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>1316</v>
+        <v>1497</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>141</v>
+        <v>172</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3000,15 +3000,15 @@
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>5288</v>
+        <v>6082</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>1094</v>
+        <v>1282</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>2263</v>
+        <v>2561</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3017,15 +3017,15 @@
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>8919</v>
+        <v>10148</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>3748</v>
+        <v>4366</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>1315</v>
+        <v>1460</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3034,15 +3034,15 @@
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>12289</v>
+        <v>14889</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>834</v>
+        <v>1009</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>473</v>
+        <v>491</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3051,15 +3051,15 @@
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>631913</v>
+        <v>722972</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>93792</v>
+        <v>108404</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>91372</v>
+        <v>104915</v>
       </c>
     </row>
   </sheetData>
@@ -11323,11 +11323,15 @@
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46235</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21">
+        <v>46265</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -11347,449 +11351,785 @@
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3">
+        <v>5873</v>
+      </c>
+      <c r="C3" s="3">
+        <v>822</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1052</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2">
+        <v>3492</v>
+      </c>
+      <c r="C4" s="2">
+        <v>238</v>
+      </c>
+      <c r="D4" s="2">
+        <v>479</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B5" s="3">
+        <v>8917</v>
+      </c>
+      <c r="C5" s="3">
+        <v>962</v>
+      </c>
+      <c r="D5" s="3">
+        <v>843</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2">
+        <v>179</v>
+      </c>
+      <c r="C6" s="2">
+        <v>99</v>
+      </c>
+      <c r="D6" s="2">
+        <v>12</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="3">
+        <v>6153</v>
+      </c>
+      <c r="C7" s="3">
+        <v>882</v>
+      </c>
+      <c r="D7" s="3">
+        <v>701</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2">
+        <v>881</v>
+      </c>
+      <c r="C8" s="2">
+        <v>141</v>
+      </c>
+      <c r="D8" s="2">
+        <v>200</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="3">
+        <v>451</v>
+      </c>
+      <c r="C9" s="3">
+        <v>112</v>
+      </c>
+      <c r="D9" s="3">
+        <v>93</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="2">
+        <v>376</v>
+      </c>
+      <c r="C10" s="2">
+        <v>35</v>
+      </c>
+      <c r="D10" s="2">
+        <v>24</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="3">
+        <v>50</v>
+      </c>
+      <c r="C11" s="3">
+        <v>25</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="4">
+        <v>57</v>
+      </c>
+      <c r="C13" s="4">
+        <v>49</v>
+      </c>
+      <c r="D13" s="4">
+        <v>1</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>187</v>
+      </c>
+      <c r="C14" s="5">
+        <v>112</v>
+      </c>
+      <c r="D14" s="5">
+        <v>41</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="B15" s="4">
+        <v>672</v>
+      </c>
+      <c r="C15" s="4">
+        <v>241</v>
+      </c>
+      <c r="D15" s="4">
+        <v>105</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="5">
+        <v>313</v>
+      </c>
+      <c r="C16" s="5">
+        <v>280</v>
+      </c>
+      <c r="D16" s="5">
+        <v>44</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="B17" s="3">
+        <v>328</v>
+      </c>
+      <c r="C17" s="3">
+        <v>120</v>
+      </c>
+      <c r="D17" s="3">
+        <v>51</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="2">
+        <v>2087</v>
+      </c>
+      <c r="C18" s="2">
+        <v>417</v>
+      </c>
+      <c r="D18" s="2">
+        <v>551</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="B19" s="3">
+        <v>138</v>
+      </c>
+      <c r="C19" s="3">
+        <v>74</v>
+      </c>
+      <c r="D19" s="3">
+        <v>39</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="2">
+        <v>2227</v>
+      </c>
+      <c r="C20" s="2">
+        <v>199</v>
+      </c>
+      <c r="D20" s="2">
+        <v>337</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B21" s="3">
+        <v>40</v>
+      </c>
+      <c r="C21" s="3">
+        <v>33</v>
+      </c>
+      <c r="D21" s="3">
+        <v>7</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="2">
+        <v>2206</v>
+      </c>
+      <c r="C22" s="2">
+        <v>303</v>
+      </c>
+      <c r="D22" s="2">
+        <v>468</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="B23" s="3">
+        <v>303</v>
+      </c>
+      <c r="C23" s="3">
+        <v>172</v>
+      </c>
+      <c r="D23" s="3">
+        <v>55</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24" s="2">
+        <v>3256</v>
+      </c>
+      <c r="C24" s="2">
+        <v>401</v>
+      </c>
+      <c r="D24" s="2">
+        <v>614</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="3">
+        <v>13704</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1105</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1427</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="B26" s="2">
+        <v>755</v>
+      </c>
+      <c r="C26" s="2">
+        <v>291</v>
+      </c>
+      <c r="D26" s="2">
+        <v>119</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="2">
+        <v>561</v>
+      </c>
+      <c r="C28" s="2">
+        <v>143</v>
+      </c>
+      <c r="D28" s="2">
+        <v>122</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="B29" s="3">
+        <v>476</v>
+      </c>
+      <c r="C29" s="3">
+        <v>94</v>
+      </c>
+      <c r="D29" s="3">
+        <v>142</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="2">
+        <v>2181</v>
+      </c>
+      <c r="C30" s="2">
+        <v>376</v>
+      </c>
+      <c r="D30" s="2">
+        <v>443</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="B31" s="3">
+        <v>52</v>
+      </c>
+      <c r="C31" s="3">
+        <v>16</v>
+      </c>
+      <c r="D31" s="3">
+        <v>17</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="2">
+        <v>184</v>
+      </c>
+      <c r="C32" s="2">
+        <v>248</v>
+      </c>
+      <c r="D32" s="2">
+        <v>13</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="B33" s="3">
+        <v>1855</v>
+      </c>
+      <c r="C33" s="3">
+        <v>444</v>
+      </c>
+      <c r="D33" s="3">
+        <v>394</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="2">
+        <v>1337</v>
+      </c>
+      <c r="C34" s="2">
+        <v>336</v>
+      </c>
+      <c r="D34" s="2">
+        <v>265</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="B35" s="3">
+        <v>771</v>
+      </c>
+      <c r="C35" s="3">
+        <v>112</v>
+      </c>
+      <c r="D35" s="3">
+        <v>119</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="B36" s="2">
+        <v>7276</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1212</v>
+      </c>
+      <c r="D36" s="2">
+        <v>1022</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="B37" s="3">
+        <v>860</v>
+      </c>
+      <c r="C37" s="3">
+        <v>504</v>
+      </c>
+      <c r="D37" s="3">
+        <v>148</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="B38" s="2">
+        <v>4036</v>
+      </c>
+      <c r="C38" s="2">
+        <v>287</v>
+      </c>
+      <c r="D38" s="2">
+        <v>475</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="B39" s="3">
+        <v>201</v>
+      </c>
+      <c r="C39" s="3">
+        <v>162</v>
+      </c>
+      <c r="D39" s="3">
+        <v>31</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="6">
+        <v>538</v>
+      </c>
+      <c r="C40" s="6">
+        <v>54</v>
+      </c>
+      <c r="D40" s="6">
+        <v>4</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="B41" s="7">
+        <v>1671</v>
+      </c>
+      <c r="C41" s="7">
+        <v>86</v>
+      </c>
+      <c r="D41" s="7">
+        <v>9</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
+      <c r="B42" s="6">
+        <v>43</v>
+      </c>
+      <c r="C42" s="6">
+        <v>18</v>
+      </c>
+      <c r="D42" s="6">
+        <v>7</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+      <c r="B43" s="7">
+        <v>348</v>
+      </c>
+      <c r="C43" s="7">
+        <v>28</v>
+      </c>
+      <c r="D43" s="7">
+        <v>6</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="B44" s="2">
+        <v>142</v>
+      </c>
+      <c r="C44" s="2">
+        <v>83</v>
+      </c>
+      <c r="D44" s="2">
+        <v>69</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="B45" s="3">
+        <v>255</v>
+      </c>
+      <c r="C45" s="3">
+        <v>149</v>
+      </c>
+      <c r="D45" s="3">
+        <v>43</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="B46" s="2">
+        <v>2096</v>
+      </c>
+      <c r="C46" s="2">
+        <v>468</v>
+      </c>
+      <c r="D46" s="2">
+        <v>455</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
+      <c r="B47" s="3">
+        <v>3826</v>
+      </c>
+      <c r="C47" s="3">
+        <v>571</v>
+      </c>
+      <c r="D47" s="3">
+        <v>606</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="B48" s="2">
+        <v>1676</v>
+      </c>
+      <c r="C48" s="2">
+        <v>458</v>
+      </c>
+      <c r="D48" s="2">
+        <v>167</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="B49" s="3">
+        <v>1192</v>
+      </c>
+      <c r="C49" s="3">
+        <v>173</v>
+      </c>
+      <c r="D49" s="3">
+        <v>311</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="B50" s="2">
+        <v>4243</v>
+      </c>
+      <c r="C50" s="2">
+        <v>487</v>
+      </c>
+      <c r="D50" s="2">
+        <v>624</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="B51" s="3">
+        <v>433</v>
+      </c>
+      <c r="C51" s="3">
+        <v>134</v>
+      </c>
+      <c r="D51" s="3">
+        <v>109</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="B52" s="2">
+        <v>1091</v>
+      </c>
+      <c r="C52" s="2">
+        <v>316</v>
+      </c>
+      <c r="D52" s="2">
+        <v>292</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="B53" s="3">
+        <v>104</v>
+      </c>
+      <c r="C53" s="3">
+        <v>171</v>
+      </c>
+      <c r="D53" s="3">
+        <v>58</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="B54" s="2">
+        <v>172</v>
+      </c>
+      <c r="C54" s="2">
+        <v>181</v>
+      </c>
+      <c r="D54" s="2">
+        <v>31</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="B55" s="3">
+        <v>794</v>
+      </c>
+      <c r="C55" s="3">
+        <v>188</v>
+      </c>
+      <c r="D55" s="3">
+        <v>298</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+      <c r="B56" s="4">
+        <v>1229</v>
+      </c>
+      <c r="C56" s="4">
+        <v>618</v>
+      </c>
+      <c r="D56" s="4">
+        <v>145</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
+      <c r="B57" s="7">
+        <v>2600</v>
+      </c>
+      <c r="C57" s="7">
+        <v>175</v>
+      </c>
+      <c r="D57" s="7">
+        <v>18</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>91059</v>
+      </c>
+      <c r="C58" s="8">
+        <v>14612</v>
+      </c>
+      <c r="D58" s="8">
+        <v>13543</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000008000000}"/>

--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Staff\Documents\GitHub\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F79ACC-56A0-4E19-A219-EA02126292EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{311A5341-B8A0-4D63-B1F4-B5C1747D2A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2075,13 +2075,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -2093,10 +2093,10 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>46265</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -2110,160 +2110,160 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>47175</v>
+        <v>53543</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>6775</v>
+        <v>7534</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>8355</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+        <v>9539</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>28048</v>
+        <v>31305</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>2267</v>
+        <v>2532</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>3953</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>72486</v>
+        <v>81070</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>6586</v>
+        <v>7455</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>6469</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7305</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>1459</v>
+        <v>1560</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>650</v>
+        <v>722</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>108</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>51907</v>
+        <v>57916</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>6497</v>
+        <v>7308</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>5693</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+        <v>6484</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>6856</v>
+        <v>7989</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>1106</v>
+        <v>1234</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>1232</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>4231</v>
+        <v>4716</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>1005</v>
+        <v>1118</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>797</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>2493</v>
+        <v>2775</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>320</v>
+        <v>363</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>184</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -2280,245 +2280,245 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>328</v>
+        <v>374</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>1431</v>
+        <v>1541</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>803</v>
+        <v>937</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>381</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>5772</v>
+        <v>6530</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>1833</v>
+        <v>2071</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>959</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>2617</v>
+        <v>2845</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>1836</v>
+        <v>2120</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>418</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>2454</v>
+        <v>2787</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>1000</v>
+        <v>1174</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>369</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>16676</v>
+        <v>18705</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>2676</v>
+        <v>2974</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>3851</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4313</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>1438</v>
+        <v>1637</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>546</v>
+        <v>661</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>347</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>17898</v>
+        <v>20421</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>1904</v>
+        <v>2092</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>2931</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3314</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
-        <v>14</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>16821</v>
+        <v>19079</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>2440</v>
+        <v>2830</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>3292</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3767</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>2935</v>
+        <v>3315</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>1354</v>
+        <v>1612</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>511</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>23552</v>
+        <v>26424</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>3409</v>
+        <v>3807</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>4004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4655</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>100614</v>
+        <v>113527</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>8284</v>
+        <v>9314</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>10394</v>
-      </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+        <v>11748</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>4962</v>
+        <v>5609</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>2011</v>
+        <v>2234</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>969</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1088</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -2535,531 +2535,531 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>5250</v>
+        <v>5674</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>1061</v>
+        <v>1262</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>1176</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1274</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>3864</v>
+        <v>4658</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>688</v>
+        <v>776</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>989</v>
-      </c>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1172</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>23049</v>
+        <v>25650</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>2832</v>
+        <v>3209</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>4200</v>
-      </c>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+        <v>4652</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>194</v>
-      </c>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>3119</v>
+        <v>3377</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>1751</v>
+        <v>1972</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>558</v>
-      </c>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>14253</v>
+        <v>16200</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>3156</v>
+        <v>3708</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>2788</v>
-      </c>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3224</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>10384</v>
+        <v>11527</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>2036</v>
+        <v>2289</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>2003</v>
-      </c>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2212</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>5444</v>
+        <v>5661</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
         <v>943</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>53844</v>
+        <v>60624</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>9222</v>
+        <v>10533</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>6981</v>
-      </c>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+        <v>7845</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>7713</v>
+        <v>8447</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>3516</v>
+        <v>3945</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>31902</v>
+        <v>35459</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>2118</v>
+        <v>2450</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>3405</v>
-      </c>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>2558</v>
+        <v>2861</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>1135</v>
+        <v>1305</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>290</v>
-      </c>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
       <c r="B40" s="6">
         <f>SUM(January:December!B40)</f>
-        <v>2547</v>
+        <v>3229</v>
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>348</v>
+        <v>471</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
-        <v>63</v>
-      </c>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
       <c r="B41" s="7">
         <f>SUM(January:December!B41)</f>
-        <v>10640</v>
+        <v>12796</v>
       </c>
       <c r="C41" s="7">
         <f>SUM(January:December!C41)</f>
-        <v>514</v>
+        <v>668</v>
       </c>
       <c r="D41" s="7">
         <f>SUM(January:December!D41)</f>
-        <v>422</v>
-      </c>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D42" s="6">
         <f>SUM(January:December!D42)</f>
-        <v>24</v>
-      </c>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
       <c r="B43" s="7">
         <f>SUM(January:December!B43)</f>
-        <v>1485</v>
+        <v>1929</v>
       </c>
       <c r="C43" s="7">
         <f>SUM(January:December!C43)</f>
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="D43" s="7">
         <f>SUM(January:December!D43)</f>
-        <v>87</v>
-      </c>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>1813</v>
+        <v>2060</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>575</v>
+        <v>654</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>998</v>
-      </c>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>3314</v>
+        <v>3544</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>1216</v>
+        <v>1382</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>322</v>
-      </c>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>15373</v>
+        <v>18213</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>3641</v>
+        <v>4106</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>3109</v>
-      </c>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+        <v>3518</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>32818</v>
+        <v>36649</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>4012</v>
+        <v>4610</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>4594</v>
-      </c>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5040</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>14526</v>
+        <v>16189</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>3432</v>
+        <v>3837</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>1415</v>
-      </c>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1559</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>7685</v>
+        <v>8785</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>1456</v>
+        <v>1601</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2168</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>34490</v>
+        <v>38604</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>3323</v>
+        <v>3743</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>5346</v>
-      </c>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+        <v>5982</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>3957</v>
+        <v>4445</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>940</v>
+        <v>1082</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>848</v>
-      </c>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>10319</v>
+        <v>11337</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>2191</v>
+        <v>2484</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>2615</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2828</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>1427</v>
+        <v>1642</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>1350</v>
+        <v>1549</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>559</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>1732</v>
+        <v>1958</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>1497</v>
+        <v>1605</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>172</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>6082</v>
+        <v>6695</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>1282</v>
+        <v>1478</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>2561</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+        <v>2777</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>10148</v>
+        <v>11290</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>4366</v>
+        <v>5028</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>1460</v>
-      </c>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+        <v>1698</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>14889</v>
+        <v>18208</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>1009</v>
+        <v>1327</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>491</v>
-      </c>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>722972</v>
+        <v>813276</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>108404</v>
+        <v>122812</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>104915</v>
+        <v>118264</v>
       </c>
     </row>
   </sheetData>
@@ -3557,23 +3557,27 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0900-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46266</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D1" s="21">
+        <v>46295</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -3587,453 +3591,789 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="3">
+        <v>6368</v>
+      </c>
+      <c r="C3" s="3">
+        <v>759</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="2">
+        <v>3257</v>
+      </c>
+      <c r="C4" s="2">
+        <v>265</v>
+      </c>
+      <c r="D4" s="2">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="3">
+        <v>8584</v>
+      </c>
+      <c r="C5" s="3">
+        <v>869</v>
+      </c>
+      <c r="D5" s="3">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="2">
+        <v>101</v>
+      </c>
+      <c r="C6" s="2">
+        <v>72</v>
+      </c>
+      <c r="D6" s="2">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B7" s="3">
+        <v>6009</v>
+      </c>
+      <c r="C7" s="3">
+        <v>811</v>
+      </c>
+      <c r="D7" s="3">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B8" s="2">
+        <v>1133</v>
+      </c>
+      <c r="C8" s="2">
+        <v>128</v>
+      </c>
+      <c r="D8" s="2">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B9" s="3">
+        <v>485</v>
+      </c>
+      <c r="C9" s="3">
+        <v>113</v>
+      </c>
+      <c r="D9" s="3">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B10" s="2">
+        <v>282</v>
+      </c>
+      <c r="C10" s="2">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B11" s="3">
+        <v>42</v>
+      </c>
+      <c r="C11" s="3">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B13" s="4">
+        <v>46</v>
+      </c>
+      <c r="C13" s="4">
+        <v>55</v>
+      </c>
+      <c r="D13" s="4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
+        <v>110</v>
+      </c>
+      <c r="C14" s="5">
+        <v>134</v>
+      </c>
+      <c r="D14" s="5">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B15" s="4">
+        <v>758</v>
+      </c>
+      <c r="C15" s="4">
+        <v>238</v>
+      </c>
+      <c r="D15" s="4">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B16" s="5">
+        <v>228</v>
+      </c>
+      <c r="C16" s="5">
+        <v>284</v>
+      </c>
+      <c r="D16" s="5">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B17" s="3">
+        <v>333</v>
+      </c>
+      <c r="C17" s="3">
+        <v>174</v>
+      </c>
+      <c r="D17" s="3">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B18" s="2">
+        <v>2029</v>
+      </c>
+      <c r="C18" s="2">
+        <v>298</v>
+      </c>
+      <c r="D18" s="2">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B19" s="3">
+        <v>199</v>
+      </c>
+      <c r="C19" s="3">
+        <v>115</v>
+      </c>
+      <c r="D19" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B20" s="2">
+        <v>2523</v>
+      </c>
+      <c r="C20" s="2">
+        <v>188</v>
+      </c>
+      <c r="D20" s="2">
+        <v>383</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
-    </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B21" s="3">
+        <v>45</v>
+      </c>
+      <c r="C21" s="3">
+        <v>38</v>
+      </c>
+      <c r="D21" s="3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
-    </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B22" s="2">
+        <v>2258</v>
+      </c>
+      <c r="C22" s="2">
+        <v>390</v>
+      </c>
+      <c r="D22" s="2">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-    </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B23" s="3">
+        <v>380</v>
+      </c>
+      <c r="C23" s="3">
+        <v>258</v>
+      </c>
+      <c r="D23" s="3">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B24" s="2">
+        <v>2872</v>
+      </c>
+      <c r="C24" s="2">
+        <v>398</v>
+      </c>
+      <c r="D24" s="2">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B25" s="3">
+        <v>12913</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1030</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1354</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B26" s="2">
+        <v>647</v>
+      </c>
+      <c r="C26" s="2">
+        <v>223</v>
+      </c>
+      <c r="D26" s="2">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
-    </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B28" s="2">
+        <v>424</v>
+      </c>
+      <c r="C28" s="2">
+        <v>201</v>
+      </c>
+      <c r="D28" s="2">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
-    </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B29" s="3">
+        <v>794</v>
+      </c>
+      <c r="C29" s="3">
+        <v>88</v>
+      </c>
+      <c r="D29" s="3">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B30" s="2">
+        <v>2601</v>
+      </c>
+      <c r="C30" s="2">
+        <v>377</v>
+      </c>
+      <c r="D30" s="2">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
-    </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B31" s="3">
+        <v>40</v>
+      </c>
+      <c r="C31" s="3">
+        <v>18</v>
+      </c>
+      <c r="D31" s="3">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-    </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B32" s="2">
+        <v>258</v>
+      </c>
+      <c r="C32" s="2">
+        <v>221</v>
+      </c>
+      <c r="D32" s="2">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
-    </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B33" s="3">
+        <v>1947</v>
+      </c>
+      <c r="C33" s="3">
+        <v>552</v>
+      </c>
+      <c r="D33" s="3">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-    </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="2">
+        <v>1143</v>
+      </c>
+      <c r="C34" s="2">
+        <v>253</v>
+      </c>
+      <c r="D34" s="2">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-    </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B35" s="3">
+        <v>217</v>
+      </c>
+      <c r="C35" s="3">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
-    </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B36" s="2">
+        <v>6780</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1311</v>
+      </c>
+      <c r="D36" s="2">
+        <v>864</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
-    </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B37" s="3">
+        <v>734</v>
+      </c>
+      <c r="C37" s="3">
+        <v>429</v>
+      </c>
+      <c r="D37" s="3">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
-    </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B38" s="2">
+        <v>3557</v>
+      </c>
+      <c r="C38" s="2">
+        <v>332</v>
+      </c>
+      <c r="D38" s="2">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
-    </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B39" s="3">
+        <v>303</v>
+      </c>
+      <c r="C39" s="3">
+        <v>170</v>
+      </c>
+      <c r="D39" s="3">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
-    </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B40" s="6">
+        <v>682</v>
+      </c>
+      <c r="C40" s="6">
+        <v>123</v>
+      </c>
+      <c r="D40" s="6">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
-    </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B41" s="7">
+        <v>2156</v>
+      </c>
+      <c r="C41" s="7">
+        <v>154</v>
+      </c>
+      <c r="D41" s="7">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-    </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B42" s="6">
+        <v>37</v>
+      </c>
+      <c r="C42" s="6">
+        <v>15</v>
+      </c>
+      <c r="D42" s="6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
-    </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B43" s="7">
+        <v>444</v>
+      </c>
+      <c r="C43" s="7">
+        <v>39</v>
+      </c>
+      <c r="D43" s="7">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
-    </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B44" s="2">
+        <v>247</v>
+      </c>
+      <c r="C44" s="2">
+        <v>79</v>
+      </c>
+      <c r="D44" s="2">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-    </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B45" s="3">
+        <v>230</v>
+      </c>
+      <c r="C45" s="3">
+        <v>166</v>
+      </c>
+      <c r="D45" s="3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
-    </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B46" s="2">
+        <v>2840</v>
+      </c>
+      <c r="C46" s="2">
+        <v>465</v>
+      </c>
+      <c r="D46" s="2">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-    </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B47" s="3">
+        <v>3831</v>
+      </c>
+      <c r="C47" s="3">
+        <v>598</v>
+      </c>
+      <c r="D47" s="3">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
-    </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B48" s="2">
+        <v>1663</v>
+      </c>
+      <c r="C48" s="2">
+        <v>405</v>
+      </c>
+      <c r="D48" s="2">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
-    </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="C49" s="3">
+        <v>145</v>
+      </c>
+      <c r="D49" s="3">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
-    </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B50" s="2">
+        <v>4114</v>
+      </c>
+      <c r="C50" s="2">
+        <v>420</v>
+      </c>
+      <c r="D50" s="2">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-    </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B51" s="3">
+        <v>488</v>
+      </c>
+      <c r="C51" s="3">
+        <v>142</v>
+      </c>
+      <c r="D51" s="3">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B52" s="2">
+        <v>1018</v>
+      </c>
+      <c r="C52" s="2">
+        <v>293</v>
+      </c>
+      <c r="D52" s="2">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B53" s="3">
+        <v>215</v>
+      </c>
+      <c r="C53" s="3">
+        <v>199</v>
+      </c>
+      <c r="D53" s="3">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B54" s="2">
+        <v>226</v>
+      </c>
+      <c r="C54" s="2">
+        <v>108</v>
+      </c>
+      <c r="D54" s="2">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B55" s="3">
+        <v>613</v>
+      </c>
+      <c r="C55" s="3">
+        <v>196</v>
+      </c>
+      <c r="D55" s="3">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
-    </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B56" s="4">
+        <v>1142</v>
+      </c>
+      <c r="C56" s="4">
+        <v>662</v>
+      </c>
+      <c r="D56" s="4">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
-    </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B57" s="7">
+        <v>3319</v>
+      </c>
+      <c r="C57" s="7">
+        <v>318</v>
+      </c>
+      <c r="D57" s="7">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>90304</v>
+      </c>
+      <c r="C58" s="8">
+        <v>14408</v>
+      </c>
+      <c r="D58" s="8">
+        <v>13349</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
@@ -4044,13 +4384,13 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0A00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4060,7 +4400,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4074,7 +4414,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4082,7 +4422,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4090,7 +4430,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4098,7 +4438,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4106,7 +4446,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4114,7 +4454,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4122,7 +4462,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4130,7 +4470,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4138,7 +4478,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4146,7 +4486,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4154,7 +4494,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4162,7 +4502,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4170,7 +4510,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4178,7 +4518,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4186,7 +4526,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4194,7 +4534,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4202,7 +4542,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4210,7 +4550,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4218,7 +4558,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4226,7 +4566,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4234,7 +4574,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4242,7 +4582,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4250,7 +4590,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4258,7 +4598,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4266,7 +4606,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4274,7 +4614,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4282,7 +4622,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4290,7 +4630,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4298,7 +4638,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4306,7 +4646,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4314,7 +4654,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4322,7 +4662,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4330,7 +4670,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4338,7 +4678,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4346,7 +4686,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4354,7 +4694,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4362,7 +4702,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4370,7 +4710,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4378,7 +4718,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4386,7 +4726,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4394,7 +4734,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4402,7 +4742,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4410,7 +4750,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4418,7 +4758,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4426,7 +4766,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4434,7 +4774,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4442,7 +4782,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4450,7 +4790,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4458,7 +4798,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4466,7 +4806,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4474,7 +4814,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4482,7 +4822,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4490,7 +4830,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4498,7 +4838,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4506,7 +4846,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -4514,7 +4854,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -4531,13 +4871,13 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0B00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -4547,7 +4887,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -4561,7 +4901,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -4569,7 +4909,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -4577,7 +4917,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -4585,7 +4925,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -4593,7 +4933,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -4601,7 +4941,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -4609,7 +4949,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -4617,7 +4957,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -4625,7 +4965,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -4633,7 +4973,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -4641,7 +4981,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -4649,7 +4989,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -4657,7 +4997,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -4665,7 +5005,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -4673,7 +5013,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -4681,7 +5021,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -4689,7 +5029,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -4697,7 +5037,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -4705,7 +5045,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -4713,7 +5053,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -4721,7 +5061,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -4729,7 +5069,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -4737,7 +5077,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -4745,7 +5085,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -4753,7 +5093,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -4761,7 +5101,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -4769,7 +5109,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -4777,7 +5117,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -4785,7 +5125,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -4793,7 +5133,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -4801,7 +5141,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -4809,7 +5149,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -4817,7 +5157,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -4825,7 +5165,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -4833,7 +5173,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -4841,7 +5181,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -4849,7 +5189,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -4857,7 +5197,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -4865,7 +5205,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -4873,7 +5213,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -4881,7 +5221,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -4889,7 +5229,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -4897,7 +5237,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -4905,7 +5245,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -4913,7 +5253,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -4921,7 +5261,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -4929,7 +5269,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -4937,7 +5277,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -4945,7 +5285,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -4953,7 +5293,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -4961,7 +5301,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -4969,7 +5309,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -4977,7 +5317,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -4985,7 +5325,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -4993,7 +5333,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -5001,7 +5341,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5018,13 +5358,13 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0C00-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5034,7 +5374,7 @@
       </c>
       <c r="D1" s="21"/>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5048,7 +5388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5056,7 +5396,7 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5064,7 +5404,7 @@
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5072,7 +5412,7 @@
       <c r="C5" s="3"/>
       <c r="D5" s="3"/>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5080,7 +5420,7 @@
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5088,7 +5428,7 @@
       <c r="C7" s="3"/>
       <c r="D7" s="3"/>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5096,7 +5436,7 @@
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5104,7 +5444,7 @@
       <c r="C9" s="3"/>
       <c r="D9" s="3"/>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5112,7 +5452,7 @@
       <c r="C10" s="2"/>
       <c r="D10" s="2"/>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5120,7 +5460,7 @@
       <c r="C11" s="3"/>
       <c r="D11" s="3"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5128,7 +5468,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5136,7 +5476,7 @@
       <c r="C13" s="4"/>
       <c r="D13" s="4"/>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5144,7 +5484,7 @@
       <c r="C14" s="5"/>
       <c r="D14" s="5"/>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5152,7 +5492,7 @@
       <c r="C15" s="4"/>
       <c r="D15" s="4"/>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5160,7 +5500,7 @@
       <c r="C16" s="5"/>
       <c r="D16" s="5"/>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5168,7 +5508,7 @@
       <c r="C17" s="3"/>
       <c r="D17" s="3"/>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5176,7 +5516,7 @@
       <c r="C18" s="2"/>
       <c r="D18" s="2"/>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5184,7 +5524,7 @@
       <c r="C19" s="3"/>
       <c r="D19" s="3"/>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5192,7 +5532,7 @@
       <c r="C20" s="2"/>
       <c r="D20" s="2"/>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5200,7 +5540,7 @@
       <c r="C21" s="3"/>
       <c r="D21" s="3"/>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5208,7 +5548,7 @@
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5216,7 +5556,7 @@
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5224,7 +5564,7 @@
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5232,7 +5572,7 @@
       <c r="C25" s="3"/>
       <c r="D25" s="3"/>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5240,7 +5580,7 @@
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5248,7 +5588,7 @@
       <c r="C27" s="3"/>
       <c r="D27" s="3"/>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5256,7 +5596,7 @@
       <c r="C28" s="2"/>
       <c r="D28" s="2"/>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5264,7 +5604,7 @@
       <c r="C29" s="3"/>
       <c r="D29" s="3"/>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5272,7 +5612,7 @@
       <c r="C30" s="2"/>
       <c r="D30" s="2"/>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5280,7 +5620,7 @@
       <c r="C31" s="3"/>
       <c r="D31" s="3"/>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5288,7 +5628,7 @@
       <c r="C32" s="2"/>
       <c r="D32" s="2"/>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5296,7 +5636,7 @@
       <c r="C33" s="3"/>
       <c r="D33" s="3"/>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5304,7 +5644,7 @@
       <c r="C34" s="2"/>
       <c r="D34" s="2"/>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -5312,7 +5652,7 @@
       <c r="C35" s="3"/>
       <c r="D35" s="3"/>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -5320,7 +5660,7 @@
       <c r="C36" s="2"/>
       <c r="D36" s="2"/>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -5328,7 +5668,7 @@
       <c r="C37" s="3"/>
       <c r="D37" s="3"/>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -5336,7 +5676,7 @@
       <c r="C38" s="2"/>
       <c r="D38" s="2"/>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -5344,7 +5684,7 @@
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -5352,7 +5692,7 @@
       <c r="C40" s="6"/>
       <c r="D40" s="6"/>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -5360,7 +5700,7 @@
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -5368,7 +5708,7 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -5376,7 +5716,7 @@
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -5384,7 +5724,7 @@
       <c r="C44" s="2"/>
       <c r="D44" s="2"/>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -5392,7 +5732,7 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -5400,7 +5740,7 @@
       <c r="C46" s="2"/>
       <c r="D46" s="2"/>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -5408,7 +5748,7 @@
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -5416,7 +5756,7 @@
       <c r="C48" s="2"/>
       <c r="D48" s="2"/>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -5424,7 +5764,7 @@
       <c r="C49" s="3"/>
       <c r="D49" s="3"/>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -5432,7 +5772,7 @@
       <c r="C50" s="2"/>
       <c r="D50" s="2"/>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -5440,7 +5780,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="3"/>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -5448,7 +5788,7 @@
       <c r="C52" s="2"/>
       <c r="D52" s="2"/>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -5456,7 +5796,7 @@
       <c r="C53" s="3"/>
       <c r="D53" s="3"/>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -5464,7 +5804,7 @@
       <c r="C54" s="2"/>
       <c r="D54" s="2"/>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -5472,7 +5812,7 @@
       <c r="C55" s="3"/>
       <c r="D55" s="3"/>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -5480,7 +5820,7 @@
       <c r="C56" s="4"/>
       <c r="D56" s="4"/>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -5488,7 +5828,7 @@
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -5504,13 +5844,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -5524,7 +5864,7 @@
         <v>46053</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -5538,7 +5878,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -5552,7 +5892,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -5566,7 +5906,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -5580,7 +5920,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -5594,7 +5934,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -5608,7 +5948,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -5622,7 +5962,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -5636,7 +5976,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -5650,7 +5990,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -5664,7 +6004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -5678,7 +6018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -5692,7 +6032,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -5706,7 +6046,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -5720,7 +6060,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -5734,7 +6074,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -5748,7 +6088,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -5762,7 +6102,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -5776,7 +6116,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -5790,7 +6130,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -5804,7 +6144,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -5818,7 +6158,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -5832,7 +6172,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -5846,7 +6186,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -5860,7 +6200,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -5874,7 +6214,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -5888,7 +6228,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -5902,7 +6242,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -5916,7 +6256,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -5930,7 +6270,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -5944,7 +6284,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -5958,7 +6298,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -5972,7 +6312,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -5986,7 +6326,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -6000,7 +6340,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6014,7 +6354,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6028,7 +6368,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6042,7 +6382,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6056,7 +6396,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6070,7 +6410,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6084,7 +6424,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6098,7 +6438,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6112,7 +6452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6126,7 +6466,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6140,7 +6480,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6154,7 +6494,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6168,7 +6508,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -6182,7 +6522,7 @@
         <v>164</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -6196,7 +6536,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -6210,7 +6550,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -6224,7 +6564,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -6238,7 +6578,7 @@
         <v>547</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -6252,7 +6592,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -6266,7 +6606,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -6280,7 +6620,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -6294,7 +6634,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -6308,7 +6648,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -6331,13 +6671,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -6351,7 +6691,7 @@
         <v>46081</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -6365,7 +6705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -6379,7 +6719,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -6393,7 +6733,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -6407,7 +6747,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -6421,7 +6761,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -6435,7 +6775,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -6449,7 +6789,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -6463,7 +6803,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -6477,7 +6817,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -6491,7 +6831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -6505,7 +6845,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -6519,7 +6859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -6533,7 +6873,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -6547,7 +6887,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -6561,7 +6901,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -6575,7 +6915,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -6589,7 +6929,7 @@
         <v>480</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -6603,7 +6943,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -6617,7 +6957,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -6631,7 +6971,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -6645,7 +6985,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -6659,7 +6999,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -6673,7 +7013,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -6687,7 +7027,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -6701,7 +7041,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -6715,7 +7055,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -6729,7 +7069,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -6743,7 +7083,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -6757,7 +7097,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -6771,7 +7111,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -6785,7 +7125,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -6799,7 +7139,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -6813,7 +7153,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -6827,7 +7167,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -6841,7 +7181,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -6855,7 +7195,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -6869,7 +7209,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -6883,7 +7223,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -6897,7 +7237,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -6911,7 +7251,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -6925,7 +7265,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -6939,7 +7279,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -6953,7 +7293,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -6967,7 +7307,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -6981,7 +7321,7 @@
         <v>358</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -6995,7 +7335,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7009,7 +7349,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7023,7 +7363,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7037,7 +7377,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7051,7 +7391,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7065,7 +7405,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7079,7 +7419,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7093,7 +7433,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7107,7 +7447,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7121,7 +7461,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7135,7 +7475,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7158,13 +7498,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:D59"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -7178,7 +7518,7 @@
         <v>46112</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -7192,7 +7532,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -7206,7 +7546,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -7220,7 +7560,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -7234,7 +7574,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -7248,7 +7588,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -7262,7 +7602,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -7276,7 +7616,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -7290,7 +7630,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -7304,7 +7644,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -7318,7 +7658,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -7332,7 +7672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -7346,7 +7686,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -7360,7 +7700,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -7374,7 +7714,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -7388,7 +7728,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -7402,7 +7742,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -7416,7 +7756,7 @@
         <v>462</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -7430,7 +7770,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -7444,7 +7784,7 @@
         <v>493</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -7458,7 +7798,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -7472,7 +7812,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -7486,7 +7826,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -7500,7 +7840,7 @@
         <v>738</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -7514,7 +7854,7 @@
         <v>1176</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -7528,7 +7868,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -7542,7 +7882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -7556,7 +7896,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -7570,7 +7910,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -7584,7 +7924,7 @@
         <v>469</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -7598,7 +7938,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -7612,7 +7952,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -7626,7 +7966,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -7640,7 +7980,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -7654,7 +7994,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -7668,7 +8008,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -7682,7 +8022,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -7696,7 +8036,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -7710,7 +8050,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -7724,7 +8064,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -7738,7 +8078,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -7752,7 +8092,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -7766,7 +8106,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -7780,7 +8120,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -7794,7 +8134,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -7808,7 +8148,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -7822,7 +8162,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -7836,7 +8176,7 @@
         <v>196</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -7850,7 +8190,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -7864,7 +8204,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -7878,7 +8218,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -7892,7 +8232,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -7906,7 +8246,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -7920,7 +8260,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -7934,7 +8274,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -7948,7 +8288,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -7962,7 +8302,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -7976,7 +8316,7 @@
         <v>13832</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>61</v>
       </c>
@@ -8000,13 +8340,13 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D61"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8020,7 +8360,7 @@
         <v>46142</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8034,7 +8374,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -8048,7 +8388,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -8062,7 +8402,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -8076,7 +8416,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -8090,7 +8430,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8104,7 +8444,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8118,7 +8458,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8132,7 +8472,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -8146,7 +8486,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8160,7 +8500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -8174,7 +8514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -8188,7 +8528,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -8202,7 +8542,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -8216,7 +8556,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -8230,7 +8570,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -8244,7 +8584,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -8258,7 +8598,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -8272,7 +8612,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -8286,7 +8626,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -8300,7 +8640,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -8314,7 +8654,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -8328,7 +8668,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -8342,7 +8682,7 @@
         <v>430</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -8356,7 +8696,7 @@
         <v>1418</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -8370,7 +8710,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -8384,7 +8724,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -8398,7 +8738,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -8412,7 +8752,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -8426,7 +8766,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -8440,7 +8780,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -8454,7 +8794,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -8468,7 +8808,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -8482,7 +8822,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -8496,7 +8836,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -8510,7 +8850,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -8524,7 +8864,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -8538,7 +8878,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -8552,7 +8892,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -8566,7 +8906,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -8580,7 +8920,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -8594,7 +8934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -8608,7 +8948,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -8622,7 +8962,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -8636,7 +8976,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -8650,7 +8990,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -8664,7 +9004,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -8678,7 +9018,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -8692,7 +9032,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -8706,7 +9046,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -8720,7 +9060,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -8734,7 +9074,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -8748,7 +9088,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -8762,7 +9102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -8776,7 +9116,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -8790,7 +9130,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -8804,7 +9144,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -8818,7 +9158,7 @@
         <v>12558</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>25</v>
       </c>
@@ -8832,13 +9172,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -8852,7 +9192,7 @@
         <v>46173</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -8866,7 +9206,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -8880,7 +9220,7 @@
         <v>891</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -8894,7 +9234,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -8908,7 +9248,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -8922,7 +9262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -8936,7 +9276,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -8950,7 +9290,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -8964,7 +9304,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -8978,7 +9318,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -8992,7 +9332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -9006,7 +9346,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -9020,7 +9360,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -9034,7 +9374,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -9048,7 +9388,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -9062,7 +9402,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -9076,7 +9416,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -9090,7 +9430,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9104,7 +9444,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -9118,7 +9458,7 @@
         <v>307</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -9132,7 +9472,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -9146,7 +9486,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -9160,7 +9500,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -9174,7 +9514,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -9188,7 +9528,7 @@
         <v>1088</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -9202,7 +9542,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -9216,7 +9556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -9230,7 +9570,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -9244,7 +9584,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -9258,7 +9598,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -9272,7 +9612,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -9286,7 +9626,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -9300,7 +9640,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -9314,7 +9654,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -9328,7 +9668,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -9342,7 +9682,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -9356,7 +9696,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -9370,7 +9710,7 @@
         <v>362</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -9384,7 +9724,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -9398,7 +9738,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -9412,7 +9752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -9426,7 +9766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -9440,7 +9780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -9454,7 +9794,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -9468,7 +9808,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -9482,7 +9822,7 @@
         <v>347</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -9496,7 +9836,7 @@
         <v>464</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -9510,7 +9850,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -9524,7 +9864,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -9538,7 +9878,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -9552,7 +9892,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -9566,7 +9906,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -9580,7 +9920,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -9594,7 +9934,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -9608,7 +9948,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -9622,7 +9962,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -9636,7 +9976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -9659,13 +9999,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -9679,7 +10019,7 @@
         <v>46203</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -9693,7 +10033,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -9707,7 +10047,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -9721,7 +10061,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -9735,7 +10075,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -9749,7 +10089,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -9763,7 +10103,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -9777,7 +10117,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -9791,7 +10131,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -9805,7 +10145,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -9819,7 +10159,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -9833,7 +10173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -9847,7 +10187,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -9861,7 +10201,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -9875,7 +10215,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -9889,7 +10229,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -9903,7 +10243,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -9917,7 +10257,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -9931,7 +10271,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -9945,7 +10285,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -9959,7 +10299,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -9973,7 +10313,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -9987,7 +10327,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -10001,7 +10341,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -10015,7 +10355,7 @@
         <v>1247</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -10029,7 +10369,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -10043,7 +10383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -10057,7 +10397,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -10071,7 +10411,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -10085,7 +10425,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -10099,7 +10439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -10113,7 +10453,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -10127,7 +10467,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -10141,7 +10481,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -10155,7 +10495,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -10169,7 +10509,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -10183,7 +10523,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -10197,7 +10537,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -10211,7 +10551,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -10225,7 +10565,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -10239,7 +10579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -10253,7 +10593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -10267,7 +10607,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -10281,7 +10621,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -10295,7 +10635,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -10309,7 +10649,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -10323,7 +10663,7 @@
         <v>529</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -10337,7 +10677,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -10351,7 +10691,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -10365,7 +10705,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -10379,7 +10719,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -10393,7 +10733,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -10407,7 +10747,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -10421,7 +10761,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -10435,7 +10775,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -10449,7 +10789,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -10463,7 +10803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -10486,13 +10826,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -10506,7 +10846,7 @@
         <v>46234</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -10520,7 +10860,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -10534,7 +10874,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -10548,7 +10888,7 @@
         <v>602</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -10562,7 +10902,7 @@
         <v>904</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -10576,7 +10916,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -10590,7 +10930,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -10604,7 +10944,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -10618,7 +10958,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -10632,7 +10972,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -10646,7 +10986,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -10660,7 +11000,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -10674,7 +11014,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -10688,7 +11028,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -10702,7 +11042,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -10716,7 +11056,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -10730,7 +11070,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -10744,7 +11084,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -10758,7 +11098,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -10772,7 +11112,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -10786,7 +11126,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -10800,7 +11140,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -10814,7 +11154,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -10828,7 +11168,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -10842,7 +11182,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -10856,7 +11196,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -10870,7 +11210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -10884,7 +11224,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -10898,7 +11238,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -10912,7 +11252,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -10926,7 +11266,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -10940,7 +11280,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -10954,7 +11294,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -10968,7 +11308,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -10982,7 +11322,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -10996,7 +11336,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -11010,7 +11350,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -11024,7 +11364,7 @@
         <v>457</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -11038,7 +11378,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -11052,7 +11392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -11066,7 +11406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -11080,7 +11420,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -11094,7 +11434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -11108,7 +11448,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -11122,7 +11462,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -11136,7 +11476,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -11150,7 +11490,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -11164,7 +11504,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -11178,7 +11518,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -11192,7 +11532,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -11206,7 +11546,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -11220,7 +11560,7 @@
         <v>250</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -11234,7 +11574,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -11248,7 +11588,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -11262,7 +11602,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -11276,7 +11616,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -11290,7 +11630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
@@ -11313,13 +11653,13 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0800-000000000000}">
   <dimension ref="A1:D58"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="50.7109375" style="1" customWidth="1"/>
-    <col min="2" max="4" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="50.6640625" style="1" customWidth="1"/>
+    <col min="2" max="4" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
@@ -11333,7 +11673,7 @@
         <v>46265</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="16" t="s">
         <v>0</v>
       </c>
@@ -11347,7 +11687,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
@@ -11361,7 +11701,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
@@ -11375,7 +11715,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
@@ -11389,7 +11729,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
@@ -11403,7 +11743,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
@@ -11417,7 +11757,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
@@ -11431,7 +11771,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
@@ -11445,7 +11785,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
@@ -11459,7 +11799,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
@@ -11473,7 +11813,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
@@ -11487,7 +11827,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
@@ -11501,7 +11841,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
@@ -11515,7 +11855,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
@@ -11529,7 +11869,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
@@ -11543,7 +11883,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
@@ -11557,7 +11897,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
@@ -11571,7 +11911,7 @@
         <v>551</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
@@ -11585,7 +11925,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
@@ -11599,7 +11939,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
@@ -11613,7 +11953,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
@@ -11627,7 +11967,7 @@
         <v>468</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
@@ -11641,7 +11981,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
@@ -11655,7 +11995,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
@@ -11669,7 +12009,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
@@ -11683,7 +12023,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
@@ -11697,7 +12037,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
@@ -11711,7 +12051,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
@@ -11725,7 +12065,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
@@ -11739,7 +12079,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
@@ -11753,7 +12093,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
@@ -11767,7 +12107,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
@@ -11781,7 +12121,7 @@
         <v>394</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
@@ -11795,7 +12135,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
@@ -11809,7 +12149,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
@@ -11823,7 +12163,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
@@ -11837,7 +12177,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
@@ -11851,7 +12191,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
@@ -11865,7 +12205,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
@@ -11879,7 +12219,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
@@ -11893,7 +12233,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
@@ -11907,7 +12247,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
@@ -11921,7 +12261,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
@@ -11935,7 +12275,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
@@ -11949,7 +12289,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
@@ -11963,7 +12303,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
@@ -11977,7 +12317,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
@@ -11991,7 +12331,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
@@ -12005,7 +12345,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
@@ -12019,7 +12359,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
@@ -12033,7 +12373,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
@@ -12047,7 +12387,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
@@ -12061,7 +12401,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
@@ -12075,7 +12415,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
@@ -12089,7 +12429,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
@@ -12103,7 +12443,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
@@ -12117,7 +12457,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>

--- a/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
+++ b/statistics_files/nekls_executive_board/2026/2026_next_statistics.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\George\Documents\github\next_statistics\statistics_files\nekls_executive_board\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0F79ACC-56A0-4E19-A219-EA02126292EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F67C7C0D-D0D1-45A6-914F-405F76E55407}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="57480" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Annual totals" sheetId="1" r:id="rId1"/>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="D1" s="21">
         <f>MAX(January:December!D1)</f>
-        <v>46265</v>
+        <v>46295</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -2116,15 +2116,15 @@
       </c>
       <c r="B3" s="3">
         <f>SUM(January:December!B3)</f>
-        <v>47175</v>
+        <v>53543</v>
       </c>
       <c r="C3" s="3">
         <f>SUM(January:December!C3)</f>
-        <v>6775</v>
+        <v>7534</v>
       </c>
       <c r="D3" s="3">
         <f>SUM(January:December!D3)</f>
-        <v>8355</v>
+        <v>9539</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
@@ -2133,15 +2133,15 @@
       </c>
       <c r="B4" s="2">
         <f>SUM(January:December!B4)</f>
-        <v>28048</v>
+        <v>31305</v>
       </c>
       <c r="C4" s="2">
         <f>SUM(January:December!C4)</f>
-        <v>2267</v>
+        <v>2532</v>
       </c>
       <c r="D4" s="2">
         <f>SUM(January:December!D4)</f>
-        <v>3953</v>
+        <v>4464</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -2150,15 +2150,15 @@
       </c>
       <c r="B5" s="3">
         <f>SUM(January:December!B5)</f>
-        <v>72486</v>
+        <v>81070</v>
       </c>
       <c r="C5" s="3">
         <f>SUM(January:December!C5)</f>
-        <v>6586</v>
+        <v>7455</v>
       </c>
       <c r="D5" s="3">
         <f>SUM(January:December!D5)</f>
-        <v>6469</v>
+        <v>7305</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -2167,15 +2167,15 @@
       </c>
       <c r="B6" s="2">
         <f>SUM(January:December!B6)</f>
-        <v>1459</v>
+        <v>1560</v>
       </c>
       <c r="C6" s="2">
         <f>SUM(January:December!C6)</f>
-        <v>650</v>
+        <v>722</v>
       </c>
       <c r="D6" s="2">
         <f>SUM(January:December!D6)</f>
-        <v>108</v>
+        <v>127</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -2184,15 +2184,15 @@
       </c>
       <c r="B7" s="3">
         <f>SUM(January:December!B7)</f>
-        <v>51907</v>
+        <v>57916</v>
       </c>
       <c r="C7" s="3">
         <f>SUM(January:December!C7)</f>
-        <v>6497</v>
+        <v>7308</v>
       </c>
       <c r="D7" s="3">
         <f>SUM(January:December!D7)</f>
-        <v>5693</v>
+        <v>6484</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -2201,15 +2201,15 @@
       </c>
       <c r="B8" s="2">
         <f>SUM(January:December!B8)</f>
-        <v>6856</v>
+        <v>7989</v>
       </c>
       <c r="C8" s="2">
         <f>SUM(January:December!C8)</f>
-        <v>1106</v>
+        <v>1234</v>
       </c>
       <c r="D8" s="2">
         <f>SUM(January:December!D8)</f>
-        <v>1232</v>
+        <v>1479</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -2218,15 +2218,15 @@
       </c>
       <c r="B9" s="3">
         <f>SUM(January:December!B9)</f>
-        <v>4231</v>
+        <v>4716</v>
       </c>
       <c r="C9" s="3">
         <f>SUM(January:December!C9)</f>
-        <v>1005</v>
+        <v>1118</v>
       </c>
       <c r="D9" s="3">
         <f>SUM(January:December!D9)</f>
-        <v>797</v>
+        <v>912</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -2235,15 +2235,15 @@
       </c>
       <c r="B10" s="2">
         <f>SUM(January:December!B10)</f>
-        <v>2493</v>
+        <v>2775</v>
       </c>
       <c r="C10" s="2">
         <f>SUM(January:December!C10)</f>
-        <v>320</v>
+        <v>363</v>
       </c>
       <c r="D10" s="2">
         <f>SUM(January:December!D10)</f>
-        <v>184</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -2252,11 +2252,11 @@
       </c>
       <c r="B11" s="3">
         <f>SUM(January:December!B11)</f>
-        <v>432</v>
+        <v>474</v>
       </c>
       <c r="C11" s="3">
         <f>SUM(January:December!C11)</f>
-        <v>137</v>
+        <v>156</v>
       </c>
       <c r="D11" s="3">
         <f>SUM(January:December!D11)</f>
@@ -2286,15 +2286,15 @@
       </c>
       <c r="B13" s="4">
         <f>SUM(January:December!B13)</f>
-        <v>328</v>
+        <v>374</v>
       </c>
       <c r="C13" s="4">
         <f>SUM(January:December!C13)</f>
-        <v>288</v>
+        <v>343</v>
       </c>
       <c r="D13" s="4">
         <f>SUM(January:December!D13)</f>
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -2303,15 +2303,15 @@
       </c>
       <c r="B14" s="5">
         <f>SUM(January:December!B14)</f>
-        <v>1431</v>
+        <v>1541</v>
       </c>
       <c r="C14" s="5">
         <f>SUM(January:December!C14)</f>
-        <v>803</v>
+        <v>937</v>
       </c>
       <c r="D14" s="5">
         <f>SUM(January:December!D14)</f>
-        <v>381</v>
+        <v>414</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -2320,15 +2320,15 @@
       </c>
       <c r="B15" s="4">
         <f>SUM(January:December!B15)</f>
-        <v>5772</v>
+        <v>6530</v>
       </c>
       <c r="C15" s="4">
         <f>SUM(January:December!C15)</f>
-        <v>1833</v>
+        <v>2071</v>
       </c>
       <c r="D15" s="4">
         <f>SUM(January:December!D15)</f>
-        <v>959</v>
+        <v>1140</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -2337,15 +2337,15 @@
       </c>
       <c r="B16" s="5">
         <f>SUM(January:December!B16)</f>
-        <v>2617</v>
+        <v>2845</v>
       </c>
       <c r="C16" s="5">
         <f>SUM(January:December!C16)</f>
-        <v>1836</v>
+        <v>2120</v>
       </c>
       <c r="D16" s="5">
         <f>SUM(January:December!D16)</f>
-        <v>418</v>
+        <v>476</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -2354,15 +2354,15 @@
       </c>
       <c r="B17" s="3">
         <f>SUM(January:December!B17)</f>
-        <v>2454</v>
+        <v>2787</v>
       </c>
       <c r="C17" s="3">
         <f>SUM(January:December!C17)</f>
-        <v>1000</v>
+        <v>1174</v>
       </c>
       <c r="D17" s="3">
         <f>SUM(January:December!D17)</f>
-        <v>369</v>
+        <v>433</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -2371,15 +2371,15 @@
       </c>
       <c r="B18" s="2">
         <f>SUM(January:December!B18)</f>
-        <v>16676</v>
+        <v>18705</v>
       </c>
       <c r="C18" s="2">
         <f>SUM(January:December!C18)</f>
-        <v>2676</v>
+        <v>2974</v>
       </c>
       <c r="D18" s="2">
         <f>SUM(January:December!D18)</f>
-        <v>3851</v>
+        <v>4313</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -2388,15 +2388,15 @@
       </c>
       <c r="B19" s="3">
         <f>SUM(January:December!B19)</f>
-        <v>1438</v>
+        <v>1637</v>
       </c>
       <c r="C19" s="3">
         <f>SUM(January:December!C19)</f>
-        <v>546</v>
+        <v>661</v>
       </c>
       <c r="D19" s="3">
         <f>SUM(January:December!D19)</f>
-        <v>347</v>
+        <v>412</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -2405,15 +2405,15 @@
       </c>
       <c r="B20" s="2">
         <f>SUM(January:December!B20)</f>
-        <v>17898</v>
+        <v>20421</v>
       </c>
       <c r="C20" s="2">
         <f>SUM(January:December!C20)</f>
-        <v>1904</v>
+        <v>2092</v>
       </c>
       <c r="D20" s="2">
         <f>SUM(January:December!D20)</f>
-        <v>2931</v>
+        <v>3314</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -2422,15 +2422,15 @@
       </c>
       <c r="B21" s="3">
         <f>SUM(January:December!B21)</f>
-        <v>182</v>
+        <v>227</v>
       </c>
       <c r="C21" s="3">
         <f>SUM(January:December!C21)</f>
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="D21" s="3">
         <f>SUM(January:December!D21)</f>
-        <v>14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -2439,15 +2439,15 @@
       </c>
       <c r="B22" s="2">
         <f>SUM(January:December!B22)</f>
-        <v>16821</v>
+        <v>19079</v>
       </c>
       <c r="C22" s="2">
         <f>SUM(January:December!C22)</f>
-        <v>2440</v>
+        <v>2830</v>
       </c>
       <c r="D22" s="2">
         <f>SUM(January:December!D22)</f>
-        <v>3292</v>
+        <v>3767</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -2456,15 +2456,15 @@
       </c>
       <c r="B23" s="3">
         <f>SUM(January:December!B23)</f>
-        <v>2935</v>
+        <v>3315</v>
       </c>
       <c r="C23" s="3">
         <f>SUM(January:December!C23)</f>
-        <v>1354</v>
+        <v>1612</v>
       </c>
       <c r="D23" s="3">
         <f>SUM(January:December!D23)</f>
-        <v>511</v>
+        <v>568</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -2473,15 +2473,15 @@
       </c>
       <c r="B24" s="2">
         <f>SUM(January:December!B24)</f>
-        <v>23552</v>
+        <v>26424</v>
       </c>
       <c r="C24" s="2">
         <f>SUM(January:December!C24)</f>
-        <v>3409</v>
+        <v>3807</v>
       </c>
       <c r="D24" s="2">
         <f>SUM(January:December!D24)</f>
-        <v>4004</v>
+        <v>4655</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -2490,15 +2490,15 @@
       </c>
       <c r="B25" s="3">
         <f>SUM(January:December!B25)</f>
-        <v>100614</v>
+        <v>113527</v>
       </c>
       <c r="C25" s="3">
         <f>SUM(January:December!C25)</f>
-        <v>8284</v>
+        <v>9314</v>
       </c>
       <c r="D25" s="3">
         <f>SUM(January:December!D25)</f>
-        <v>10394</v>
+        <v>11748</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -2507,15 +2507,15 @@
       </c>
       <c r="B26" s="2">
         <f>SUM(January:December!B26)</f>
-        <v>4962</v>
+        <v>5609</v>
       </c>
       <c r="C26" s="2">
         <f>SUM(January:December!C26)</f>
-        <v>2011</v>
+        <v>2234</v>
       </c>
       <c r="D26" s="2">
         <f>SUM(January:December!D26)</f>
-        <v>969</v>
+        <v>1088</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -2541,15 +2541,15 @@
       </c>
       <c r="B28" s="2">
         <f>SUM(January:December!B28)</f>
-        <v>5250</v>
+        <v>5674</v>
       </c>
       <c r="C28" s="2">
         <f>SUM(January:December!C28)</f>
-        <v>1061</v>
+        <v>1262</v>
       </c>
       <c r="D28" s="2">
         <f>SUM(January:December!D28)</f>
-        <v>1176</v>
+        <v>1274</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -2558,15 +2558,15 @@
       </c>
       <c r="B29" s="3">
         <f>SUM(January:December!B29)</f>
-        <v>3864</v>
+        <v>4658</v>
       </c>
       <c r="C29" s="3">
         <f>SUM(January:December!C29)</f>
-        <v>688</v>
+        <v>776</v>
       </c>
       <c r="D29" s="3">
         <f>SUM(January:December!D29)</f>
-        <v>989</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -2575,15 +2575,15 @@
       </c>
       <c r="B30" s="2">
         <f>SUM(January:December!B30)</f>
-        <v>23049</v>
+        <v>25650</v>
       </c>
       <c r="C30" s="2">
         <f>SUM(January:December!C30)</f>
-        <v>2832</v>
+        <v>3209</v>
       </c>
       <c r="D30" s="2">
         <f>SUM(January:December!D30)</f>
-        <v>4200</v>
+        <v>4652</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -2592,15 +2592,15 @@
       </c>
       <c r="B31" s="3">
         <f>SUM(January:December!B31)</f>
-        <v>400</v>
+        <v>440</v>
       </c>
       <c r="C31" s="3">
         <f>SUM(January:December!C31)</f>
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="D31" s="3">
         <f>SUM(January:December!D31)</f>
-        <v>194</v>
+        <v>212</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
@@ -2609,15 +2609,15 @@
       </c>
       <c r="B32" s="2">
         <f>SUM(January:December!B32)</f>
-        <v>3119</v>
+        <v>3377</v>
       </c>
       <c r="C32" s="2">
         <f>SUM(January:December!C32)</f>
-        <v>1751</v>
+        <v>1972</v>
       </c>
       <c r="D32" s="2">
         <f>SUM(January:December!D32)</f>
-        <v>558</v>
+        <v>604</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -2626,15 +2626,15 @@
       </c>
       <c r="B33" s="3">
         <f>SUM(January:December!B33)</f>
-        <v>14253</v>
+        <v>16200</v>
       </c>
       <c r="C33" s="3">
         <f>SUM(January:December!C33)</f>
-        <v>3156</v>
+        <v>3708</v>
       </c>
       <c r="D33" s="3">
         <f>SUM(January:December!D33)</f>
-        <v>2788</v>
+        <v>3224</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
@@ -2643,15 +2643,15 @@
       </c>
       <c r="B34" s="2">
         <f>SUM(January:December!B34)</f>
-        <v>10384</v>
+        <v>11527</v>
       </c>
       <c r="C34" s="2">
         <f>SUM(January:December!C34)</f>
-        <v>2036</v>
+        <v>2289</v>
       </c>
       <c r="D34" s="2">
         <f>SUM(January:December!D34)</f>
-        <v>2003</v>
+        <v>2212</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -2660,11 +2660,11 @@
       </c>
       <c r="B35" s="3">
         <f>SUM(January:December!B35)</f>
-        <v>5444</v>
+        <v>5661</v>
       </c>
       <c r="C35" s="3">
         <f>SUM(January:December!C35)</f>
-        <v>719</v>
+        <v>726</v>
       </c>
       <c r="D35" s="3">
         <f>SUM(January:December!D35)</f>
@@ -2677,15 +2677,15 @@
       </c>
       <c r="B36" s="2">
         <f>SUM(January:December!B36)</f>
-        <v>53844</v>
+        <v>60624</v>
       </c>
       <c r="C36" s="2">
         <f>SUM(January:December!C36)</f>
-        <v>9222</v>
+        <v>10533</v>
       </c>
       <c r="D36" s="2">
         <f>SUM(January:December!D36)</f>
-        <v>6981</v>
+        <v>7845</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -2694,15 +2694,15 @@
       </c>
       <c r="B37" s="3">
         <f>SUM(January:December!B37)</f>
-        <v>7713</v>
+        <v>8447</v>
       </c>
       <c r="C37" s="3">
         <f>SUM(January:December!C37)</f>
-        <v>3516</v>
+        <v>3945</v>
       </c>
       <c r="D37" s="3">
         <f>SUM(January:December!D37)</f>
-        <v>1076</v>
+        <v>1203</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -2711,15 +2711,15 @@
       </c>
       <c r="B38" s="2">
         <f>SUM(January:December!B38)</f>
-        <v>31902</v>
+        <v>35459</v>
       </c>
       <c r="C38" s="2">
         <f>SUM(January:December!C38)</f>
-        <v>2118</v>
+        <v>2450</v>
       </c>
       <c r="D38" s="2">
         <f>SUM(January:December!D38)</f>
-        <v>3405</v>
+        <v>3838</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
@@ -2728,15 +2728,15 @@
       </c>
       <c r="B39" s="3">
         <f>SUM(January:December!B39)</f>
-        <v>2558</v>
+        <v>2861</v>
       </c>
       <c r="C39" s="3">
         <f>SUM(January:December!C39)</f>
-        <v>1135</v>
+        <v>1305</v>
       </c>
       <c r="D39" s="3">
         <f>SUM(January:December!D39)</f>
-        <v>290</v>
+        <v>322</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -2745,15 +2745,15 @@
       </c>
       <c r="B40" s="6">
         <f>SUM(January:December!B40)</f>
-        <v>2547</v>
+        <v>3229</v>
       </c>
       <c r="C40" s="6">
         <f>SUM(January:December!C40)</f>
-        <v>348</v>
+        <v>471</v>
       </c>
       <c r="D40" s="6">
         <f>SUM(January:December!D40)</f>
-        <v>63</v>
+        <v>76</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
@@ -2762,15 +2762,15 @@
       </c>
       <c r="B41" s="7">
         <f>SUM(January:December!B41)</f>
-        <v>10640</v>
+        <v>12796</v>
       </c>
       <c r="C41" s="7">
         <f>SUM(January:December!C41)</f>
-        <v>514</v>
+        <v>668</v>
       </c>
       <c r="D41" s="7">
         <f>SUM(January:December!D41)</f>
-        <v>422</v>
+        <v>487</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
@@ -2779,15 +2779,15 @@
       </c>
       <c r="B42" s="6">
         <f>SUM(January:December!B42)</f>
-        <v>217</v>
+        <v>254</v>
       </c>
       <c r="C42" s="6">
         <f>SUM(January:December!C42)</f>
-        <v>111</v>
+        <v>126</v>
       </c>
       <c r="D42" s="6">
         <f>SUM(January:December!D42)</f>
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -2796,15 +2796,15 @@
       </c>
       <c r="B43" s="7">
         <f>SUM(January:December!B43)</f>
-        <v>1485</v>
+        <v>1929</v>
       </c>
       <c r="C43" s="7">
         <f>SUM(January:December!C43)</f>
-        <v>144</v>
+        <v>183</v>
       </c>
       <c r="D43" s="7">
         <f>SUM(January:December!D43)</f>
-        <v>87</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -2813,15 +2813,15 @@
       </c>
       <c r="B44" s="2">
         <f>SUM(January:December!B44)</f>
-        <v>1813</v>
+        <v>2060</v>
       </c>
       <c r="C44" s="2">
         <f>SUM(January:December!C44)</f>
-        <v>575</v>
+        <v>654</v>
       </c>
       <c r="D44" s="2">
         <f>SUM(January:December!D44)</f>
-        <v>998</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
@@ -2830,15 +2830,15 @@
       </c>
       <c r="B45" s="3">
         <f>SUM(January:December!B45)</f>
-        <v>3314</v>
+        <v>3544</v>
       </c>
       <c r="C45" s="3">
         <f>SUM(January:December!C45)</f>
-        <v>1216</v>
+        <v>1382</v>
       </c>
       <c r="D45" s="3">
         <f>SUM(January:December!D45)</f>
-        <v>322</v>
+        <v>346</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
@@ -2847,15 +2847,15 @@
       </c>
       <c r="B46" s="2">
         <f>SUM(January:December!B46)</f>
-        <v>15373</v>
+        <v>18213</v>
       </c>
       <c r="C46" s="2">
         <f>SUM(January:December!C46)</f>
-        <v>3641</v>
+        <v>4106</v>
       </c>
       <c r="D46" s="2">
         <f>SUM(January:December!D46)</f>
-        <v>3109</v>
+        <v>3518</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -2864,15 +2864,15 @@
       </c>
       <c r="B47" s="3">
         <f>SUM(January:December!B47)</f>
-        <v>32818</v>
+        <v>36649</v>
       </c>
       <c r="C47" s="3">
         <f>SUM(January:December!C47)</f>
-        <v>4012</v>
+        <v>4610</v>
       </c>
       <c r="D47" s="3">
         <f>SUM(January:December!D47)</f>
-        <v>4594</v>
+        <v>5040</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -2881,15 +2881,15 @@
       </c>
       <c r="B48" s="2">
         <f>SUM(January:December!B48)</f>
-        <v>14526</v>
+        <v>16189</v>
       </c>
       <c r="C48" s="2">
         <f>SUM(January:December!C48)</f>
-        <v>3432</v>
+        <v>3837</v>
       </c>
       <c r="D48" s="2">
         <f>SUM(January:December!D48)</f>
-        <v>1415</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -2898,15 +2898,15 @@
       </c>
       <c r="B49" s="3">
         <f>SUM(January:December!B49)</f>
-        <v>7685</v>
+        <v>8785</v>
       </c>
       <c r="C49" s="3">
         <f>SUM(January:December!C49)</f>
-        <v>1456</v>
+        <v>1601</v>
       </c>
       <c r="D49" s="3">
         <f>SUM(January:December!D49)</f>
-        <v>1912</v>
+        <v>2168</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -2915,15 +2915,15 @@
       </c>
       <c r="B50" s="2">
         <f>SUM(January:December!B50)</f>
-        <v>34490</v>
+        <v>38604</v>
       </c>
       <c r="C50" s="2">
         <f>SUM(January:December!C50)</f>
-        <v>3323</v>
+        <v>3743</v>
       </c>
       <c r="D50" s="2">
         <f>SUM(January:December!D50)</f>
-        <v>5346</v>
+        <v>5982</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -2932,15 +2932,15 @@
       </c>
       <c r="B51" s="3">
         <f>SUM(January:December!B51)</f>
-        <v>3957</v>
+        <v>4445</v>
       </c>
       <c r="C51" s="3">
         <f>SUM(January:December!C51)</f>
-        <v>940</v>
+        <v>1082</v>
       </c>
       <c r="D51" s="3">
         <f>SUM(January:December!D51)</f>
-        <v>848</v>
+        <v>987</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -2949,15 +2949,15 @@
       </c>
       <c r="B52" s="2">
         <f>SUM(January:December!B52)</f>
-        <v>10319</v>
+        <v>11337</v>
       </c>
       <c r="C52" s="2">
         <f>SUM(January:December!C52)</f>
-        <v>2191</v>
+        <v>2484</v>
       </c>
       <c r="D52" s="2">
         <f>SUM(January:December!D52)</f>
-        <v>2615</v>
+        <v>2828</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -2966,15 +2966,15 @@
       </c>
       <c r="B53" s="3">
         <f>SUM(January:December!B53)</f>
-        <v>1427</v>
+        <v>1642</v>
       </c>
       <c r="C53" s="3">
         <f>SUM(January:December!C53)</f>
-        <v>1350</v>
+        <v>1549</v>
       </c>
       <c r="D53" s="3">
         <f>SUM(January:December!D53)</f>
-        <v>559</v>
+        <v>624</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -2983,15 +2983,15 @@
       </c>
       <c r="B54" s="2">
         <f>SUM(January:December!B54)</f>
-        <v>1732</v>
+        <v>1958</v>
       </c>
       <c r="C54" s="2">
         <f>SUM(January:December!C54)</f>
-        <v>1497</v>
+        <v>1605</v>
       </c>
       <c r="D54" s="2">
         <f>SUM(January:December!D54)</f>
-        <v>172</v>
+        <v>192</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -3000,15 +3000,15 @@
       </c>
       <c r="B55" s="3">
         <f>SUM(January:December!B55)</f>
-        <v>6082</v>
+        <v>6695</v>
       </c>
       <c r="C55" s="3">
         <f>SUM(January:December!C55)</f>
-        <v>1282</v>
+        <v>1478</v>
       </c>
       <c r="D55" s="3">
         <f>SUM(January:December!D55)</f>
-        <v>2561</v>
+        <v>2777</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -3017,15 +3017,15 @@
       </c>
       <c r="B56" s="4">
         <f>SUM(January:December!B56)</f>
-        <v>10148</v>
+        <v>11290</v>
       </c>
       <c r="C56" s="4">
         <f>SUM(January:December!C56)</f>
-        <v>4366</v>
+        <v>5028</v>
       </c>
       <c r="D56" s="4">
         <f>SUM(January:December!D56)</f>
-        <v>1460</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -3034,15 +3034,15 @@
       </c>
       <c r="B57" s="7">
         <f>SUM(January:December!B57)</f>
-        <v>14889</v>
+        <v>18208</v>
       </c>
       <c r="C57" s="7">
         <f>SUM(January:December!C57)</f>
-        <v>1009</v>
+        <v>1327</v>
       </c>
       <c r="D57" s="7">
         <f>SUM(January:December!D57)</f>
-        <v>491</v>
+        <v>573</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -3051,15 +3051,15 @@
       </c>
       <c r="B58" s="8">
         <f>SUM(January:December!B58)</f>
-        <v>722972</v>
+        <v>813276</v>
       </c>
       <c r="C58" s="8">
         <f>SUM(January:December!C58)</f>
-        <v>108404</v>
+        <v>122812</v>
       </c>
       <c r="D58" s="8">
         <f>SUM(January:December!D58)</f>
-        <v>104915</v>
+        <v>118264</v>
       </c>
     </row>
   </sheetData>
@@ -3567,11 +3567,15 @@
       <c r="A1" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="19"/>
+      <c r="B1" s="19">
+        <v>46266</v>
+      </c>
       <c r="C1" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="D1" s="21"/>
+      <c r="D1" s="21">
+        <v>46295</v>
+      </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -3591,449 +3595,785 @@
       <c r="A3" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
+      <c r="B3" s="3">
+        <v>6368</v>
+      </c>
+      <c r="C3" s="3">
+        <v>759</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1184</v>
+      </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
+      <c r="B4" s="2">
+        <v>3257</v>
+      </c>
+      <c r="C4" s="2">
+        <v>265</v>
+      </c>
+      <c r="D4" s="2">
+        <v>511</v>
+      </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
+      <c r="B5" s="3">
+        <v>8584</v>
+      </c>
+      <c r="C5" s="3">
+        <v>869</v>
+      </c>
+      <c r="D5" s="3">
+        <v>836</v>
+      </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
+      <c r="B6" s="2">
+        <v>101</v>
+      </c>
+      <c r="C6" s="2">
+        <v>72</v>
+      </c>
+      <c r="D6" s="2">
+        <v>19</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
+      <c r="B7" s="3">
+        <v>6009</v>
+      </c>
+      <c r="C7" s="3">
+        <v>811</v>
+      </c>
+      <c r="D7" s="3">
+        <v>791</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
+      <c r="B8" s="2">
+        <v>1133</v>
+      </c>
+      <c r="C8" s="2">
+        <v>128</v>
+      </c>
+      <c r="D8" s="2">
+        <v>247</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
+      <c r="B9" s="3">
+        <v>485</v>
+      </c>
+      <c r="C9" s="3">
+        <v>113</v>
+      </c>
+      <c r="D9" s="3">
+        <v>115</v>
+      </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
+      <c r="B10" s="2">
+        <v>282</v>
+      </c>
+      <c r="C10" s="2">
+        <v>43</v>
+      </c>
+      <c r="D10" s="2">
+        <v>21</v>
+      </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
+      <c r="B11" s="3">
+        <v>42</v>
+      </c>
+      <c r="C11" s="3">
+        <v>19</v>
+      </c>
+      <c r="D11" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
+      <c r="B12" s="2">
+        <v>0</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="4"/>
-      <c r="C13" s="4"/>
-      <c r="D13" s="4"/>
+      <c r="B13" s="4">
+        <v>46</v>
+      </c>
+      <c r="C13" s="4">
+        <v>55</v>
+      </c>
+      <c r="D13" s="4">
+        <v>10</v>
+      </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B14" s="5"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
+      <c r="B14" s="5">
+        <v>110</v>
+      </c>
+      <c r="C14" s="5">
+        <v>134</v>
+      </c>
+      <c r="D14" s="5">
+        <v>33</v>
+      </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="4"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+      <c r="B15" s="4">
+        <v>758</v>
+      </c>
+      <c r="C15" s="4">
+        <v>238</v>
+      </c>
+      <c r="D15" s="4">
+        <v>181</v>
+      </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A16" s="12" t="s">
         <v>19</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
+      <c r="B16" s="5">
+        <v>228</v>
+      </c>
+      <c r="C16" s="5">
+        <v>284</v>
+      </c>
+      <c r="D16" s="5">
+        <v>58</v>
+      </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
+      <c r="B17" s="3">
+        <v>333</v>
+      </c>
+      <c r="C17" s="3">
+        <v>174</v>
+      </c>
+      <c r="D17" s="3">
+        <v>64</v>
+      </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="B18" s="2"/>
-      <c r="C18" s="2"/>
-      <c r="D18" s="2"/>
+      <c r="B18" s="2">
+        <v>2029</v>
+      </c>
+      <c r="C18" s="2">
+        <v>298</v>
+      </c>
+      <c r="D18" s="2">
+        <v>462</v>
+      </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-      <c r="D19" s="3"/>
+      <c r="B19" s="3">
+        <v>199</v>
+      </c>
+      <c r="C19" s="3">
+        <v>115</v>
+      </c>
+      <c r="D19" s="3">
+        <v>65</v>
+      </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="B20" s="2"/>
-      <c r="C20" s="2"/>
-      <c r="D20" s="2"/>
+      <c r="B20" s="2">
+        <v>2523</v>
+      </c>
+      <c r="C20" s="2">
+        <v>188</v>
+      </c>
+      <c r="D20" s="2">
+        <v>383</v>
+      </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="B21" s="3"/>
-      <c r="C21" s="3"/>
-      <c r="D21" s="3"/>
+      <c r="B21" s="3">
+        <v>45</v>
+      </c>
+      <c r="C21" s="3">
+        <v>38</v>
+      </c>
+      <c r="D21" s="3">
+        <v>6</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="B22" s="2"/>
-      <c r="C22" s="2"/>
-      <c r="D22" s="2"/>
+      <c r="B22" s="2">
+        <v>2258</v>
+      </c>
+      <c r="C22" s="2">
+        <v>390</v>
+      </c>
+      <c r="D22" s="2">
+        <v>475</v>
+      </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
+      <c r="B23" s="3">
+        <v>380</v>
+      </c>
+      <c r="C23" s="3">
+        <v>258</v>
+      </c>
+      <c r="D23" s="3">
+        <v>57</v>
+      </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="2"/>
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
+      <c r="B24" s="2">
+        <v>2872</v>
+      </c>
+      <c r="C24" s="2">
+        <v>398</v>
+      </c>
+      <c r="D24" s="2">
+        <v>651</v>
+      </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B25" s="3"/>
-      <c r="C25" s="3"/>
-      <c r="D25" s="3"/>
+      <c r="B25" s="3">
+        <v>12913</v>
+      </c>
+      <c r="C25" s="3">
+        <v>1030</v>
+      </c>
+      <c r="D25" s="3">
+        <v>1354</v>
+      </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>29</v>
       </c>
-      <c r="B26" s="2"/>
-      <c r="C26" s="2"/>
-      <c r="D26" s="2"/>
+      <c r="B26" s="2">
+        <v>647</v>
+      </c>
+      <c r="C26" s="2">
+        <v>223</v>
+      </c>
+      <c r="D26" s="2">
+        <v>119</v>
+      </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B27" s="3"/>
-      <c r="C27" s="3"/>
-      <c r="D27" s="3"/>
+      <c r="B27" s="3">
+        <v>0</v>
+      </c>
+      <c r="C27" s="3">
+        <v>0</v>
+      </c>
+      <c r="D27" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" s="9" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="2"/>
-      <c r="C28" s="2"/>
-      <c r="D28" s="2"/>
+      <c r="B28" s="2">
+        <v>424</v>
+      </c>
+      <c r="C28" s="2">
+        <v>201</v>
+      </c>
+      <c r="D28" s="2">
+        <v>98</v>
+      </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="B29" s="3"/>
-      <c r="C29" s="3"/>
-      <c r="D29" s="3"/>
+      <c r="B29" s="3">
+        <v>794</v>
+      </c>
+      <c r="C29" s="3">
+        <v>88</v>
+      </c>
+      <c r="D29" s="3">
+        <v>183</v>
+      </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="B30" s="2"/>
-      <c r="C30" s="2"/>
-      <c r="D30" s="2"/>
+      <c r="B30" s="2">
+        <v>2601</v>
+      </c>
+      <c r="C30" s="2">
+        <v>377</v>
+      </c>
+      <c r="D30" s="2">
+        <v>452</v>
+      </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="B31" s="3"/>
-      <c r="C31" s="3"/>
-      <c r="D31" s="3"/>
+      <c r="B31" s="3">
+        <v>40</v>
+      </c>
+      <c r="C31" s="3">
+        <v>18</v>
+      </c>
+      <c r="D31" s="3">
+        <v>18</v>
+      </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
+      <c r="B32" s="2">
+        <v>258</v>
+      </c>
+      <c r="C32" s="2">
+        <v>221</v>
+      </c>
+      <c r="D32" s="2">
+        <v>46</v>
+      </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="B33" s="3"/>
-      <c r="C33" s="3"/>
-      <c r="D33" s="3"/>
+      <c r="B33" s="3">
+        <v>1947</v>
+      </c>
+      <c r="C33" s="3">
+        <v>552</v>
+      </c>
+      <c r="D33" s="3">
+        <v>436</v>
+      </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
+      <c r="B34" s="2">
+        <v>1143</v>
+      </c>
+      <c r="C34" s="2">
+        <v>253</v>
+      </c>
+      <c r="D34" s="2">
+        <v>209</v>
+      </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
+      <c r="B35" s="3">
+        <v>217</v>
+      </c>
+      <c r="C35" s="3">
+        <v>7</v>
+      </c>
+      <c r="D35" s="3">
+        <v>0</v>
+      </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="2"/>
-      <c r="C36" s="2"/>
-      <c r="D36" s="2"/>
+      <c r="B36" s="2">
+        <v>6780</v>
+      </c>
+      <c r="C36" s="2">
+        <v>1311</v>
+      </c>
+      <c r="D36" s="2">
+        <v>864</v>
+      </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3"/>
-      <c r="C37" s="3"/>
-      <c r="D37" s="3"/>
+      <c r="B37" s="3">
+        <v>734</v>
+      </c>
+      <c r="C37" s="3">
+        <v>429</v>
+      </c>
+      <c r="D37" s="3">
+        <v>127</v>
+      </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="2"/>
+      <c r="B38" s="2">
+        <v>3557</v>
+      </c>
+      <c r="C38" s="2">
+        <v>332</v>
+      </c>
+      <c r="D38" s="2">
+        <v>433</v>
+      </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B39" s="3"/>
-      <c r="C39" s="3"/>
-      <c r="D39" s="3"/>
+      <c r="B39" s="3">
+        <v>303</v>
+      </c>
+      <c r="C39" s="3">
+        <v>170</v>
+      </c>
+      <c r="D39" s="3">
+        <v>32</v>
+      </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="B40" s="6"/>
-      <c r="C40" s="6"/>
-      <c r="D40" s="6"/>
+      <c r="B40" s="6">
+        <v>682</v>
+      </c>
+      <c r="C40" s="6">
+        <v>123</v>
+      </c>
+      <c r="D40" s="6">
+        <v>13</v>
+      </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B41" s="7"/>
-      <c r="C41" s="7"/>
-      <c r="D41" s="7"/>
+      <c r="B41" s="7">
+        <v>2156</v>
+      </c>
+      <c r="C41" s="7">
+        <v>154</v>
+      </c>
+      <c r="D41" s="7">
+        <v>65</v>
+      </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
+      <c r="B42" s="6">
+        <v>37</v>
+      </c>
+      <c r="C42" s="6">
+        <v>15</v>
+      </c>
+      <c r="D42" s="6">
+        <v>9</v>
+      </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="B43" s="7"/>
-      <c r="C43" s="7"/>
-      <c r="D43" s="7"/>
+      <c r="B43" s="7">
+        <v>444</v>
+      </c>
+      <c r="C43" s="7">
+        <v>39</v>
+      </c>
+      <c r="D43" s="7">
+        <v>11</v>
+      </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" s="9" t="s">
         <v>47</v>
       </c>
-      <c r="B44" s="2"/>
-      <c r="C44" s="2"/>
-      <c r="D44" s="2"/>
+      <c r="B44" s="2">
+        <v>247</v>
+      </c>
+      <c r="C44" s="2">
+        <v>79</v>
+      </c>
+      <c r="D44" s="2">
+        <v>143</v>
+      </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
+      <c r="B45" s="3">
+        <v>230</v>
+      </c>
+      <c r="C45" s="3">
+        <v>166</v>
+      </c>
+      <c r="D45" s="3">
+        <v>24</v>
+      </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" s="9" t="s">
         <v>49</v>
       </c>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="2"/>
+      <c r="B46" s="2">
+        <v>2840</v>
+      </c>
+      <c r="C46" s="2">
+        <v>465</v>
+      </c>
+      <c r="D46" s="2">
+        <v>409</v>
+      </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
+      <c r="B47" s="3">
+        <v>3831</v>
+      </c>
+      <c r="C47" s="3">
+        <v>598</v>
+      </c>
+      <c r="D47" s="3">
+        <v>446</v>
+      </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="2"/>
+      <c r="B48" s="2">
+        <v>1663</v>
+      </c>
+      <c r="C48" s="2">
+        <v>405</v>
+      </c>
+      <c r="D48" s="2">
+        <v>144</v>
+      </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A49" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="D49" s="3"/>
+      <c r="B49" s="3">
+        <v>1100</v>
+      </c>
+      <c r="C49" s="3">
+        <v>145</v>
+      </c>
+      <c r="D49" s="3">
+        <v>256</v>
+      </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A50" s="9" t="s">
         <v>53</v>
       </c>
-      <c r="B50" s="2"/>
-      <c r="C50" s="2"/>
-      <c r="D50" s="2"/>
+      <c r="B50" s="2">
+        <v>4114</v>
+      </c>
+      <c r="C50" s="2">
+        <v>420</v>
+      </c>
+      <c r="D50" s="2">
+        <v>636</v>
+      </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A51" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
+      <c r="B51" s="3">
+        <v>488</v>
+      </c>
+      <c r="C51" s="3">
+        <v>142</v>
+      </c>
+      <c r="D51" s="3">
+        <v>139</v>
+      </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A52" s="9" t="s">
         <v>55</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="2"/>
+      <c r="B52" s="2">
+        <v>1018</v>
+      </c>
+      <c r="C52" s="2">
+        <v>293</v>
+      </c>
+      <c r="D52" s="2">
+        <v>213</v>
+      </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A53" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="D53" s="3"/>
+      <c r="B53" s="3">
+        <v>215</v>
+      </c>
+      <c r="C53" s="3">
+        <v>199</v>
+      </c>
+      <c r="D53" s="3">
+        <v>65</v>
+      </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A54" s="9" t="s">
         <v>57</v>
       </c>
-      <c r="B54" s="2"/>
-      <c r="C54" s="2"/>
-      <c r="D54" s="2"/>
+      <c r="B54" s="2">
+        <v>226</v>
+      </c>
+      <c r="C54" s="2">
+        <v>108</v>
+      </c>
+      <c r="D54" s="2">
+        <v>20</v>
+      </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A55" s="10" t="s">
         <v>58</v>
       </c>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="D55" s="3"/>
+      <c r="B55" s="3">
+        <v>613</v>
+      </c>
+      <c r="C55" s="3">
+        <v>196</v>
+      </c>
+      <c r="D55" s="3">
+        <v>216</v>
+      </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="B56" s="4"/>
-      <c r="C56" s="4"/>
-      <c r="D56" s="4"/>
+      <c r="B56" s="4">
+        <v>1142</v>
+      </c>
+      <c r="C56" s="4">
+        <v>662</v>
+      </c>
+      <c r="D56" s="4">
+        <v>238</v>
+      </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A57" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="B57" s="7"/>
-      <c r="C57" s="7"/>
-      <c r="D57" s="7"/>
+      <c r="B57" s="7">
+        <v>3319</v>
+      </c>
+      <c r="C57" s="7">
+        <v>318</v>
+      </c>
+      <c r="D57" s="7">
+        <v>82</v>
+      </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A58" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="B58" s="8"/>
-      <c r="C58" s="8"/>
-      <c r="D58" s="8"/>
+      <c r="B58" s="8">
+        <v>90304</v>
+      </c>
+      <c r="C58" s="8">
+        <v>14408</v>
+      </c>
+      <c r="D58" s="8">
+        <v>13349</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:D2" xr:uid="{00000000-0009-0000-0000-000009000000}"/>
